--- a/ReportHome75h.xlsx
+++ b/ReportHome75h.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacquesleooscar/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacquesleooscar/Documents/Education/ETHZ/Curriculum/Semester04/04MasterThesis/LTMM_Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3072EC9C-792E-3140-BEBD-17371916AFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D6B0A0-2899-C945-BF99-CD7BB73BA41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="760" windowWidth="15140" windowHeight="9300" tabRatio="242" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" tabRatio="242" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="75h" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="173">
   <si>
     <t>date</t>
   </si>
@@ -2967,9 +2967,7 @@
       <c r="D34" s="46">
         <v>41067</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="E34" s="2"/>
       <c r="F34" s="6"/>
       <c r="G34" s="7"/>
       <c r="H34" s="2"/>
@@ -4021,9 +4019,7 @@
       <c r="D54" s="46">
         <v>40895</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="E54" s="2"/>
       <c r="F54" s="6"/>
       <c r="G54" s="7">
         <v>0.9375</v>
@@ -4359,9 +4355,7 @@
       <c r="D61" s="46">
         <v>40882</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="E61" s="2"/>
       <c r="F61" s="6"/>
       <c r="G61" s="7">
         <v>0.625</v>
